--- a/artfynd/A 23235-2025 artfynd.xlsx
+++ b/artfynd/A 23235-2025 artfynd.xlsx
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125852445</v>
+        <v>125852437</v>
       </c>
       <c r="B12" t="n">
-        <v>57651</v>
+        <v>91220</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451346</v>
+        <v>451385</v>
       </c>
       <c r="R12" t="n">
-        <v>7058072</v>
+        <v>7057764</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,11 +1771,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125852454</v>
+        <v>125852445</v>
       </c>
       <c r="B13" t="n">
         <v>57651</v>
@@ -1837,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451369</v>
+        <v>451346</v>
       </c>
       <c r="R13" t="n">
-        <v>7057632</v>
+        <v>7058072</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125852442</v>
+        <v>125852454</v>
       </c>
       <c r="B14" t="n">
         <v>57651</v>
@@ -1939,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451256</v>
+        <v>451369</v>
       </c>
       <c r="R14" t="n">
-        <v>7057974</v>
+        <v>7057632</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125852443</v>
+        <v>125852442</v>
       </c>
       <c r="B15" t="n">
         <v>57651</v>
@@ -2041,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451354</v>
+        <v>451256</v>
       </c>
       <c r="R15" t="n">
-        <v>7058042</v>
+        <v>7057974</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2081,7 +2076,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2108,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125852447</v>
+        <v>125852443</v>
       </c>
       <c r="B16" t="n">
         <v>57651</v>
@@ -2143,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451341</v>
+        <v>451354</v>
       </c>
       <c r="R16" t="n">
-        <v>7058098</v>
+        <v>7058042</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2183,7 +2178,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2210,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125852437</v>
+        <v>125852447</v>
       </c>
       <c r="B17" t="n">
-        <v>91220</v>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2221,21 +2216,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451385</v>
+        <v>451341</v>
       </c>
       <c r="R17" t="n">
-        <v>7057764</v>
+        <v>7058098</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2281,6 +2276,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 23235-2025 artfynd.xlsx
+++ b/artfynd/A 23235-2025 artfynd.xlsx
@@ -1208,7 +1208,7 @@
         <v>125852435</v>
       </c>
       <c r="B7" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>125852436</v>
       </c>
       <c r="B10" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>125852460</v>
       </c>
       <c r="B11" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125852437</v>
+        <v>125852445</v>
       </c>
       <c r="B12" t="n">
-        <v>91220</v>
+        <v>57651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451385</v>
+        <v>451346</v>
       </c>
       <c r="R12" t="n">
-        <v>7057764</v>
+        <v>7058072</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,6 +1771,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,7 +1802,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125852445</v>
+        <v>125852454</v>
       </c>
       <c r="B13" t="n">
         <v>57651</v>
@@ -1832,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451346</v>
+        <v>451369</v>
       </c>
       <c r="R13" t="n">
-        <v>7058072</v>
+        <v>7057632</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1904,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125852454</v>
+        <v>125852442</v>
       </c>
       <c r="B14" t="n">
         <v>57651</v>
@@ -1934,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451369</v>
+        <v>451256</v>
       </c>
       <c r="R14" t="n">
-        <v>7057632</v>
+        <v>7057974</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2006,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125852442</v>
+        <v>125852443</v>
       </c>
       <c r="B15" t="n">
         <v>57651</v>
@@ -2036,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451256</v>
+        <v>451354</v>
       </c>
       <c r="R15" t="n">
-        <v>7057974</v>
+        <v>7058042</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2076,7 +2081,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,7 +2108,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125852443</v>
+        <v>125852447</v>
       </c>
       <c r="B16" t="n">
         <v>57651</v>
@@ -2138,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451354</v>
+        <v>451341</v>
       </c>
       <c r="R16" t="n">
-        <v>7058042</v>
+        <v>7058098</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2178,7 +2183,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125852447</v>
+        <v>125852437</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>91227</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2216,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2240,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451341</v>
+        <v>451385</v>
       </c>
       <c r="R17" t="n">
-        <v>7058098</v>
+        <v>7057764</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2276,11 +2281,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125852440</v>
+        <v>125852463</v>
       </c>
       <c r="B19" t="n">
-        <v>57651</v>
+        <v>91245</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2420,21 +2420,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451296</v>
+        <v>451524</v>
       </c>
       <c r="R19" t="n">
-        <v>7057765</v>
+        <v>7057967</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2480,11 +2480,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2613,10 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125852463</v>
+        <v>125852440</v>
       </c>
       <c r="B21" t="n">
-        <v>91238</v>
+        <v>57651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2624,21 +2619,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2648,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451524</v>
+        <v>451296</v>
       </c>
       <c r="R21" t="n">
-        <v>7057967</v>
+        <v>7057765</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2684,6 +2679,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2713,7 +2713,7 @@
         <v>125852461</v>
       </c>
       <c r="B22" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>125852462</v>
       </c>
       <c r="B23" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125852439</v>
+        <v>125852459</v>
       </c>
       <c r="B25" t="n">
-        <v>57651</v>
+        <v>91245</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3017,21 +3017,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3041,10 +3041,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451296</v>
+        <v>451208</v>
       </c>
       <c r="R25" t="n">
-        <v>7057721</v>
+        <v>7057705</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3077,11 +3077,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3108,10 +3103,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125852459</v>
+        <v>125852439</v>
       </c>
       <c r="B26" t="n">
-        <v>91238</v>
+        <v>57651</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3119,21 +3114,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3143,10 +3138,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451208</v>
+        <v>451296</v>
       </c>
       <c r="R26" t="n">
-        <v>7057705</v>
+        <v>7057721</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3179,6 +3174,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 23235-2025 artfynd.xlsx
+++ b/artfynd/A 23235-2025 artfynd.xlsx
@@ -1208,7 +1208,7 @@
         <v>125852435</v>
       </c>
       <c r="B7" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>125852436</v>
       </c>
       <c r="B10" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>125852460</v>
       </c>
       <c r="B11" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125852445</v>
+        <v>125852437</v>
       </c>
       <c r="B12" t="n">
-        <v>57651</v>
+        <v>91228</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451346</v>
+        <v>451385</v>
       </c>
       <c r="R12" t="n">
-        <v>7058072</v>
+        <v>7057764</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,11 +1771,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125852454</v>
+        <v>125852445</v>
       </c>
       <c r="B13" t="n">
         <v>57651</v>
@@ -1837,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451369</v>
+        <v>451346</v>
       </c>
       <c r="R13" t="n">
-        <v>7057632</v>
+        <v>7058072</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125852442</v>
+        <v>125852454</v>
       </c>
       <c r="B14" t="n">
         <v>57651</v>
@@ -1939,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451256</v>
+        <v>451369</v>
       </c>
       <c r="R14" t="n">
-        <v>7057974</v>
+        <v>7057632</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125852443</v>
+        <v>125852442</v>
       </c>
       <c r="B15" t="n">
         <v>57651</v>
@@ -2041,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451354</v>
+        <v>451256</v>
       </c>
       <c r="R15" t="n">
-        <v>7058042</v>
+        <v>7057974</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2081,7 +2076,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2108,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125852447</v>
+        <v>125852443</v>
       </c>
       <c r="B16" t="n">
         <v>57651</v>
@@ -2143,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451341</v>
+        <v>451354</v>
       </c>
       <c r="R16" t="n">
-        <v>7058098</v>
+        <v>7058042</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2183,7 +2178,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2210,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125852437</v>
+        <v>125852447</v>
       </c>
       <c r="B17" t="n">
-        <v>91227</v>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2221,21 +2216,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451385</v>
+        <v>451341</v>
       </c>
       <c r="R17" t="n">
-        <v>7057764</v>
+        <v>7058098</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2281,6 +2276,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2310,7 +2310,7 @@
         <v>125852465</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125852463</v>
+        <v>125852440</v>
       </c>
       <c r="B19" t="n">
-        <v>91245</v>
+        <v>57651</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2420,21 +2420,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451524</v>
+        <v>451296</v>
       </c>
       <c r="R19" t="n">
-        <v>7057967</v>
+        <v>7057765</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2480,6 +2480,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2506,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125852466</v>
+        <v>125852463</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>91246</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2517,21 +2522,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2541,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451456</v>
+        <v>451524</v>
       </c>
       <c r="R20" t="n">
-        <v>7058013</v>
+        <v>7057967</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2577,11 +2582,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2608,10 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125852440</v>
+        <v>125852466</v>
       </c>
       <c r="B21" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,21 +2619,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451296</v>
+        <v>451456</v>
       </c>
       <c r="R21" t="n">
-        <v>7057765</v>
+        <v>7058013</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2713,7 +2713,7 @@
         <v>125852461</v>
       </c>
       <c r="B22" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>125852462</v>
       </c>
       <c r="B23" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>125852459</v>
       </c>
       <c r="B25" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 23235-2025 artfynd.xlsx
+++ b/artfynd/A 23235-2025 artfynd.xlsx
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125852449</v>
+        <v>125852446</v>
       </c>
       <c r="B5" t="n">
         <v>57651</v>
@@ -1009,37 +1009,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>besöker bebott bo</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451463</v>
+        <v>451310</v>
       </c>
       <c r="R5" t="n">
-        <v>7057814</v>
+        <v>7058083</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1056,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Bohål i gran, ca 2,5-3 upp. Ungar hördes och båda föräldrarna kom för att ge mat.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125852446</v>
+        <v>125852449</v>
       </c>
       <c r="B6" t="n">
         <v>57651</v>
@@ -1131,17 +1111,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>besöker bebott bo</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451310</v>
+        <v>451463</v>
       </c>
       <c r="R6" t="n">
-        <v>7058083</v>
+        <v>7057814</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål i gran, ca 2,5-3 upp. Ungar hördes och båda föräldrarna kom för att ge mat.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125852437</v>
+        <v>125852445</v>
       </c>
       <c r="B12" t="n">
-        <v>91228</v>
+        <v>57651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451385</v>
+        <v>451346</v>
       </c>
       <c r="R12" t="n">
-        <v>7057764</v>
+        <v>7058072</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,6 +1771,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,7 +1802,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125852445</v>
+        <v>125852454</v>
       </c>
       <c r="B13" t="n">
         <v>57651</v>
@@ -1832,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451346</v>
+        <v>451369</v>
       </c>
       <c r="R13" t="n">
-        <v>7058072</v>
+        <v>7057632</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1904,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125852454</v>
+        <v>125852442</v>
       </c>
       <c r="B14" t="n">
         <v>57651</v>
@@ -1934,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451369</v>
+        <v>451256</v>
       </c>
       <c r="R14" t="n">
-        <v>7057632</v>
+        <v>7057974</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2006,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125852442</v>
+        <v>125852443</v>
       </c>
       <c r="B15" t="n">
         <v>57651</v>
@@ -2036,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451256</v>
+        <v>451354</v>
       </c>
       <c r="R15" t="n">
-        <v>7057974</v>
+        <v>7058042</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2076,7 +2081,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,7 +2108,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125852443</v>
+        <v>125852447</v>
       </c>
       <c r="B16" t="n">
         <v>57651</v>
@@ -2138,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451354</v>
+        <v>451341</v>
       </c>
       <c r="R16" t="n">
-        <v>7058042</v>
+        <v>7058098</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2178,7 +2183,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125852447</v>
+        <v>125852437</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>91228</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2216,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2240,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451341</v>
+        <v>451385</v>
       </c>
       <c r="R17" t="n">
-        <v>7058098</v>
+        <v>7057764</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2276,11 +2281,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125852440</v>
+        <v>125852463</v>
       </c>
       <c r="B19" t="n">
-        <v>57651</v>
+        <v>91246</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2420,21 +2420,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451296</v>
+        <v>451524</v>
       </c>
       <c r="R19" t="n">
-        <v>7057765</v>
+        <v>7057967</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2480,11 +2480,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2511,10 +2506,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125852463</v>
+        <v>125852466</v>
       </c>
       <c r="B20" t="n">
-        <v>91246</v>
+        <v>78968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2522,21 +2517,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2546,10 +2541,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451524</v>
+        <v>451456</v>
       </c>
       <c r="R20" t="n">
-        <v>7057967</v>
+        <v>7058013</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2582,6 +2577,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2608,10 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125852466</v>
+        <v>125852440</v>
       </c>
       <c r="B21" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,21 +2619,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451456</v>
+        <v>451296</v>
       </c>
       <c r="R21" t="n">
-        <v>7058013</v>
+        <v>7057765</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ganska rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 23235-2025 artfynd.xlsx
+++ b/artfynd/A 23235-2025 artfynd.xlsx
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125852450</v>
+        <v>125852449</v>
       </c>
       <c r="B4" t="n">
         <v>57651</v>
@@ -907,17 +907,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>besöker bebott bo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451428</v>
+        <v>451463</v>
       </c>
       <c r="R4" t="n">
-        <v>7057788</v>
+        <v>7057814</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +974,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Bohål i gran, ca 2,5-3 upp. Ungar hördes och båda föräldrarna kom för att ge mat.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125852446</v>
+        <v>125852450</v>
       </c>
       <c r="B5" t="n">
         <v>57651</v>
@@ -1016,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451310</v>
+        <v>451428</v>
       </c>
       <c r="R5" t="n">
-        <v>7058083</v>
+        <v>7057788</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125852449</v>
+        <v>125852446</v>
       </c>
       <c r="B6" t="n">
         <v>57651</v>
@@ -1111,37 +1131,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>besöker bebott bo</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451463</v>
+        <v>451310</v>
       </c>
       <c r="R6" t="n">
-        <v>7057814</v>
+        <v>7058083</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Bohål i gran, ca 2,5-3 upp. Ungar hördes och båda föräldrarna kom för att ge mat.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1700,7 +1700,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125852445</v>
+        <v>125852447</v>
       </c>
       <c r="B12" t="n">
         <v>57651</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451346</v>
+        <v>451341</v>
       </c>
       <c r="R12" t="n">
-        <v>7058072</v>
+        <v>7058098</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125852454</v>
+        <v>125852437</v>
       </c>
       <c r="B13" t="n">
-        <v>57651</v>
+        <v>91228</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451369</v>
+        <v>451385</v>
       </c>
       <c r="R13" t="n">
-        <v>7057632</v>
+        <v>7057764</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,11 +1873,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1904,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125852442</v>
+        <v>125852445</v>
       </c>
       <c r="B14" t="n">
         <v>57651</v>
@@ -1939,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451256</v>
+        <v>451346</v>
       </c>
       <c r="R14" t="n">
-        <v>7057974</v>
+        <v>7058072</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125852443</v>
+        <v>125852454</v>
       </c>
       <c r="B15" t="n">
         <v>57651</v>
@@ -2041,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451354</v>
+        <v>451369</v>
       </c>
       <c r="R15" t="n">
-        <v>7058042</v>
+        <v>7057632</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2081,7 +2076,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2108,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125852447</v>
+        <v>125852442</v>
       </c>
       <c r="B16" t="n">
         <v>57651</v>
@@ -2143,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451341</v>
+        <v>451256</v>
       </c>
       <c r="R16" t="n">
-        <v>7058098</v>
+        <v>7057974</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125852437</v>
+        <v>125852443</v>
       </c>
       <c r="B17" t="n">
-        <v>91228</v>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2221,21 +2216,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451385</v>
+        <v>451354</v>
       </c>
       <c r="R17" t="n">
-        <v>7057764</v>
+        <v>7058042</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2281,6 +2276,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125852463</v>
+        <v>125852440</v>
       </c>
       <c r="B19" t="n">
-        <v>91246</v>
+        <v>57651</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2420,21 +2420,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451524</v>
+        <v>451296</v>
       </c>
       <c r="R19" t="n">
-        <v>7057967</v>
+        <v>7057765</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2480,6 +2480,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2506,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125852466</v>
+        <v>125852463</v>
       </c>
       <c r="B20" t="n">
-        <v>78968</v>
+        <v>91246</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2517,21 +2522,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2541,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451456</v>
+        <v>451524</v>
       </c>
       <c r="R20" t="n">
-        <v>7058013</v>
+        <v>7057967</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2577,11 +2582,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2608,10 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125852440</v>
+        <v>125852466</v>
       </c>
       <c r="B21" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,21 +2619,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451296</v>
+        <v>451456</v>
       </c>
       <c r="R21" t="n">
-        <v>7057765</v>
+        <v>7058013</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 23235-2025 artfynd.xlsx
+++ b/artfynd/A 23235-2025 artfynd.xlsx
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125852449</v>
+        <v>125852450</v>
       </c>
       <c r="B4" t="n">
         <v>57651</v>
@@ -907,37 +907,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>besöker bebott bo</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451463</v>
+        <v>451428</v>
       </c>
       <c r="R4" t="n">
-        <v>7057814</v>
+        <v>7057788</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Bohål i gran, ca 2,5-3 upp. Ungar hördes och båda föräldrarna kom för att ge mat.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125852450</v>
+        <v>125852449</v>
       </c>
       <c r="B5" t="n">
         <v>57651</v>
@@ -1029,17 +1009,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>besöker bebott bo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451428</v>
+        <v>451463</v>
       </c>
       <c r="R5" t="n">
-        <v>7057788</v>
+        <v>7057814</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Bohål i gran, ca 2,5-3 upp. Ungar hördes och båda föräldrarna kom för att ge mat.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1208,7 +1208,7 @@
         <v>125852435</v>
       </c>
       <c r="B7" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>125852436</v>
       </c>
       <c r="B10" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>125852460</v>
       </c>
       <c r="B11" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125852447</v>
+        <v>125852445</v>
       </c>
       <c r="B12" t="n">
         <v>57651</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451341</v>
+        <v>451346</v>
       </c>
       <c r="R12" t="n">
-        <v>7058098</v>
+        <v>7058072</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125852437</v>
+        <v>125852454</v>
       </c>
       <c r="B13" t="n">
-        <v>91228</v>
+        <v>57651</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451385</v>
+        <v>451369</v>
       </c>
       <c r="R13" t="n">
-        <v>7057764</v>
+        <v>7057632</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,6 +1873,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,7 +1904,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125852445</v>
+        <v>125852442</v>
       </c>
       <c r="B14" t="n">
         <v>57651</v>
@@ -1934,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451346</v>
+        <v>451256</v>
       </c>
       <c r="R14" t="n">
-        <v>7058072</v>
+        <v>7057974</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2006,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125852454</v>
+        <v>125852443</v>
       </c>
       <c r="B15" t="n">
         <v>57651</v>
@@ -2036,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451369</v>
+        <v>451354</v>
       </c>
       <c r="R15" t="n">
-        <v>7057632</v>
+        <v>7058042</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2076,7 +2081,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,7 +2108,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125852442</v>
+        <v>125852447</v>
       </c>
       <c r="B16" t="n">
         <v>57651</v>
@@ -2138,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451256</v>
+        <v>451341</v>
       </c>
       <c r="R16" t="n">
-        <v>7057974</v>
+        <v>7058098</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125852443</v>
+        <v>125852437</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>91232</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2216,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2240,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451354</v>
+        <v>451385</v>
       </c>
       <c r="R17" t="n">
-        <v>7058042</v>
+        <v>7057764</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2276,11 +2281,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2310,7 +2310,7 @@
         <v>125852465</v>
       </c>
       <c r="B18" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>125852463</v>
       </c>
       <c r="B20" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>125852466</v>
       </c>
       <c r="B21" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>125852461</v>
       </c>
       <c r="B22" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>125852462</v>
       </c>
       <c r="B23" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125852459</v>
+        <v>125852439</v>
       </c>
       <c r="B25" t="n">
-        <v>91246</v>
+        <v>57651</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3017,21 +3017,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3041,10 +3041,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451208</v>
+        <v>451296</v>
       </c>
       <c r="R25" t="n">
-        <v>7057705</v>
+        <v>7057721</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3077,6 +3077,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3103,10 +3108,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125852439</v>
+        <v>125852459</v>
       </c>
       <c r="B26" t="n">
-        <v>57651</v>
+        <v>91250</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3114,21 +3119,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3138,10 +3143,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451296</v>
+        <v>451208</v>
       </c>
       <c r="R26" t="n">
-        <v>7057721</v>
+        <v>7057705</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3174,11 +3179,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 23235-2025 artfynd.xlsx
+++ b/artfynd/A 23235-2025 artfynd.xlsx
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125852440</v>
+        <v>125852463</v>
       </c>
       <c r="B19" t="n">
-        <v>57651</v>
+        <v>91250</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2420,21 +2420,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451296</v>
+        <v>451524</v>
       </c>
       <c r="R19" t="n">
-        <v>7057765</v>
+        <v>7057967</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2480,11 +2480,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2511,10 +2506,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125852463</v>
+        <v>125852466</v>
       </c>
       <c r="B20" t="n">
-        <v>91250</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2522,21 +2517,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2546,10 +2541,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451524</v>
+        <v>451456</v>
       </c>
       <c r="R20" t="n">
-        <v>7057967</v>
+        <v>7058013</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2582,6 +2577,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2608,10 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125852466</v>
+        <v>125852440</v>
       </c>
       <c r="B21" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,21 +2619,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451456</v>
+        <v>451296</v>
       </c>
       <c r="R21" t="n">
-        <v>7058013</v>
+        <v>7057765</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ganska rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3006,10 +3006,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125852439</v>
+        <v>125852459</v>
       </c>
       <c r="B25" t="n">
-        <v>57651</v>
+        <v>91250</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3017,21 +3017,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3041,10 +3041,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451296</v>
+        <v>451208</v>
       </c>
       <c r="R25" t="n">
-        <v>7057721</v>
+        <v>7057705</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3077,11 +3077,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3108,10 +3103,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125852459</v>
+        <v>125852439</v>
       </c>
       <c r="B26" t="n">
-        <v>91250</v>
+        <v>57651</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3119,21 +3114,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3143,10 +3138,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451208</v>
+        <v>451296</v>
       </c>
       <c r="R26" t="n">
-        <v>7057705</v>
+        <v>7057721</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3179,6 +3174,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 23235-2025 artfynd.xlsx
+++ b/artfynd/A 23235-2025 artfynd.xlsx
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125852445</v>
+        <v>125852437</v>
       </c>
       <c r="B12" t="n">
-        <v>57651</v>
+        <v>91232</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451346</v>
+        <v>451385</v>
       </c>
       <c r="R12" t="n">
-        <v>7058072</v>
+        <v>7057764</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,11 +1771,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125852454</v>
+        <v>125852445</v>
       </c>
       <c r="B13" t="n">
         <v>57651</v>
@@ -1837,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451369</v>
+        <v>451346</v>
       </c>
       <c r="R13" t="n">
-        <v>7057632</v>
+        <v>7058072</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125852442</v>
+        <v>125852454</v>
       </c>
       <c r="B14" t="n">
         <v>57651</v>
@@ -1939,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451256</v>
+        <v>451369</v>
       </c>
       <c r="R14" t="n">
-        <v>7057974</v>
+        <v>7057632</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125852443</v>
+        <v>125852442</v>
       </c>
       <c r="B15" t="n">
         <v>57651</v>
@@ -2041,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451354</v>
+        <v>451256</v>
       </c>
       <c r="R15" t="n">
-        <v>7058042</v>
+        <v>7057974</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2081,7 +2076,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2108,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125852447</v>
+        <v>125852443</v>
       </c>
       <c r="B16" t="n">
         <v>57651</v>
@@ -2143,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451341</v>
+        <v>451354</v>
       </c>
       <c r="R16" t="n">
-        <v>7058098</v>
+        <v>7058042</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2183,7 +2178,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2210,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125852437</v>
+        <v>125852447</v>
       </c>
       <c r="B17" t="n">
-        <v>91232</v>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2221,21 +2216,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451385</v>
+        <v>451341</v>
       </c>
       <c r="R17" t="n">
-        <v>7057764</v>
+        <v>7058098</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2281,6 +2276,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 23235-2025 artfynd.xlsx
+++ b/artfynd/A 23235-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3203,6 +3203,624 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126167777</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Enarsvedjan N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>451484</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7057699</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126167776</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91232</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Enarsvedjan N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>451409</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7058099</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126167782</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Enarsvedjan N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>451310</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7057897</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>ca 3,4 m upp i avbruten gran</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126167783</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91250</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Enarsvedjan N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>451409</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7057724</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126167784</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Enarsvedjan N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>451340</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7057968</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>ca 1,8m upp i avbruten gran</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126167778</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Enarsvedjan N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>451467</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7057708</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23235-2025 artfynd.xlsx
+++ b/artfynd/A 23235-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125852444</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125852448</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125852450</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>125852449</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>125852446</v>
       </c>
       <c r="B6" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>125852435</v>
       </c>
       <c r="B7" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>125852452</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>125852453</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>125852436</v>
       </c>
       <c r="B10" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>125852460</v>
       </c>
       <c r="B11" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>125852437</v>
       </c>
       <c r="B12" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>125852445</v>
       </c>
       <c r="B13" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>125852454</v>
       </c>
       <c r="B14" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>125852442</v>
       </c>
       <c r="B15" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>125852443</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>125852447</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>125852465</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>125852463</v>
       </c>
       <c r="B19" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>125852466</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>125852440</v>
       </c>
       <c r="B21" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>125852461</v>
       </c>
       <c r="B22" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>125852462</v>
       </c>
       <c r="B23" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>125852451</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>125852459</v>
       </c>
       <c r="B25" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>125852439</v>
       </c>
       <c r="B26" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>126167777</v>
       </c>
       <c r="B27" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>126167776</v>
       </c>
       <c r="B28" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>126167782</v>
       </c>
       <c r="B29" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>126167783</v>
       </c>
       <c r="B30" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>126167784</v>
       </c>
       <c r="B31" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>126167778</v>
       </c>
       <c r="B32" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 23235-2025 artfynd.xlsx
+++ b/artfynd/A 23235-2025 artfynd.xlsx
@@ -3006,10 +3006,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125852459</v>
+        <v>125852439</v>
       </c>
       <c r="B25" t="n">
-        <v>91252</v>
+        <v>57652</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3017,21 +3017,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3041,10 +3041,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451208</v>
+        <v>451296</v>
       </c>
       <c r="R25" t="n">
-        <v>7057705</v>
+        <v>7057721</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3077,6 +3077,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3103,10 +3108,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125852439</v>
+        <v>125852459</v>
       </c>
       <c r="B26" t="n">
-        <v>57652</v>
+        <v>91252</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3114,21 +3119,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3138,10 +3143,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451296</v>
+        <v>451208</v>
       </c>
       <c r="R26" t="n">
-        <v>7057721</v>
+        <v>7057705</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3174,11 +3179,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 23235-2025 artfynd.xlsx
+++ b/artfynd/A 23235-2025 artfynd.xlsx
@@ -1208,7 +1208,7 @@
         <v>125852435</v>
       </c>
       <c r="B7" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>125852436</v>
       </c>
       <c r="B10" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>125852460</v>
       </c>
       <c r="B11" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>125852437</v>
       </c>
       <c r="B12" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>125852463</v>
       </c>
       <c r="B19" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>125852461</v>
       </c>
       <c r="B22" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>125852462</v>
       </c>
       <c r="B23" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125852439</v>
+        <v>125852459</v>
       </c>
       <c r="B25" t="n">
-        <v>57652</v>
+        <v>91254</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3017,21 +3017,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3041,10 +3041,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451296</v>
+        <v>451208</v>
       </c>
       <c r="R25" t="n">
-        <v>7057721</v>
+        <v>7057705</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3077,11 +3077,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3108,10 +3103,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125852459</v>
+        <v>125852439</v>
       </c>
       <c r="B26" t="n">
-        <v>91252</v>
+        <v>57652</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3119,21 +3114,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3143,10 +3138,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451208</v>
+        <v>451296</v>
       </c>
       <c r="R26" t="n">
-        <v>7057705</v>
+        <v>7057721</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3179,6 +3174,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3310,7 +3310,7 @@
         <v>126167776</v>
       </c>
       <c r="B28" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>126167783</v>
       </c>
       <c r="B30" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 23235-2025 artfynd.xlsx
+++ b/artfynd/A 23235-2025 artfynd.xlsx
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125852463</v>
+        <v>125852440</v>
       </c>
       <c r="B19" t="n">
-        <v>91254</v>
+        <v>57652</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2420,21 +2420,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451524</v>
+        <v>451296</v>
       </c>
       <c r="R19" t="n">
-        <v>7057967</v>
+        <v>7057765</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2480,6 +2480,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2506,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125852466</v>
+        <v>125852463</v>
       </c>
       <c r="B20" t="n">
-        <v>78973</v>
+        <v>91254</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2517,21 +2522,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2541,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451456</v>
+        <v>451524</v>
       </c>
       <c r="R20" t="n">
-        <v>7058013</v>
+        <v>7057967</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2577,11 +2582,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2608,10 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125852440</v>
+        <v>125852466</v>
       </c>
       <c r="B21" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,21 +2619,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451296</v>
+        <v>451456</v>
       </c>
       <c r="R21" t="n">
-        <v>7057765</v>
+        <v>7058013</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 23235-2025 artfynd.xlsx
+++ b/artfynd/A 23235-2025 artfynd.xlsx
@@ -1208,7 +1208,7 @@
         <v>125852435</v>
       </c>
       <c r="B7" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>125852436</v>
       </c>
       <c r="B10" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>125852460</v>
       </c>
       <c r="B11" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>125852437</v>
       </c>
       <c r="B12" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125852440</v>
+        <v>125852463</v>
       </c>
       <c r="B19" t="n">
-        <v>57652</v>
+        <v>91256</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2420,21 +2420,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451296</v>
+        <v>451524</v>
       </c>
       <c r="R19" t="n">
-        <v>7057765</v>
+        <v>7057967</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2480,11 +2480,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2511,10 +2506,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125852463</v>
+        <v>125852466</v>
       </c>
       <c r="B20" t="n">
-        <v>91254</v>
+        <v>78973</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2522,21 +2517,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2546,10 +2541,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451524</v>
+        <v>451456</v>
       </c>
       <c r="R20" t="n">
-        <v>7057967</v>
+        <v>7058013</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2582,6 +2577,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2608,10 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125852466</v>
+        <v>125852440</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,21 +2619,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451456</v>
+        <v>451296</v>
       </c>
       <c r="R21" t="n">
-        <v>7058013</v>
+        <v>7057765</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ganska rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2713,7 +2713,7 @@
         <v>125852461</v>
       </c>
       <c r="B22" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>125852462</v>
       </c>
       <c r="B23" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>125852459</v>
       </c>
       <c r="B25" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>126167776</v>
       </c>
       <c r="B28" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>126167783</v>
       </c>
       <c r="B30" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 23235-2025 artfynd.xlsx
+++ b/artfynd/A 23235-2025 artfynd.xlsx
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125852463</v>
+        <v>125852440</v>
       </c>
       <c r="B19" t="n">
-        <v>91256</v>
+        <v>57652</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2420,21 +2420,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451524</v>
+        <v>451296</v>
       </c>
       <c r="R19" t="n">
-        <v>7057967</v>
+        <v>7057765</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2480,6 +2480,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2506,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125852466</v>
+        <v>125852463</v>
       </c>
       <c r="B20" t="n">
-        <v>78973</v>
+        <v>91256</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2517,21 +2522,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2541,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451456</v>
+        <v>451524</v>
       </c>
       <c r="R20" t="n">
-        <v>7058013</v>
+        <v>7057967</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2577,11 +2582,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2608,10 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125852440</v>
+        <v>125852466</v>
       </c>
       <c r="B21" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,21 +2619,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451296</v>
+        <v>451456</v>
       </c>
       <c r="R21" t="n">
-        <v>7057765</v>
+        <v>7058013</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 23235-2025 artfynd.xlsx
+++ b/artfynd/A 23235-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125852444</v>
       </c>
       <c r="B2" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125852448</v>
       </c>
       <c r="B3" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125852450</v>
       </c>
       <c r="B4" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125852449</v>
+        <v>125852446</v>
       </c>
       <c r="B5" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,37 +1009,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>besöker bebott bo</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451463</v>
+        <v>451310</v>
       </c>
       <c r="R5" t="n">
-        <v>7057814</v>
+        <v>7058083</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1056,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Bohål i gran, ca 2,5-3 upp. Ungar hördes och båda föräldrarna kom för att ge mat.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125852446</v>
+        <v>125852449</v>
       </c>
       <c r="B6" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,17 +1111,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>besöker bebott bo</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451310</v>
+        <v>451463</v>
       </c>
       <c r="R6" t="n">
-        <v>7058083</v>
+        <v>7057814</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål i gran, ca 2,5-3 upp. Ungar hördes och båda föräldrarna kom för att ge mat.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,7 +1208,7 @@
         <v>125852435</v>
       </c>
       <c r="B7" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125852452</v>
+        <v>125852453</v>
       </c>
       <c r="B8" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451383</v>
+        <v>451364</v>
       </c>
       <c r="R8" t="n">
-        <v>7057759</v>
+        <v>7057629</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125852453</v>
+        <v>125852452</v>
       </c>
       <c r="B9" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451364</v>
+        <v>451383</v>
       </c>
       <c r="R9" t="n">
-        <v>7057629</v>
+        <v>7057759</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1509,7 +1509,7 @@
         <v>125852436</v>
       </c>
       <c r="B10" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>125852460</v>
       </c>
       <c r="B11" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>125852437</v>
       </c>
       <c r="B12" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125852445</v>
+        <v>125852447</v>
       </c>
       <c r="B13" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451346</v>
+        <v>451341</v>
       </c>
       <c r="R13" t="n">
-        <v>7058072</v>
+        <v>7058098</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125852454</v>
+        <v>125852443</v>
       </c>
       <c r="B14" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451369</v>
+        <v>451354</v>
       </c>
       <c r="R14" t="n">
-        <v>7057632</v>
+        <v>7058042</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2004,7 +2004,7 @@
         <v>125852442</v>
       </c>
       <c r="B15" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125852443</v>
+        <v>125852454</v>
       </c>
       <c r="B16" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451354</v>
+        <v>451369</v>
       </c>
       <c r="R16" t="n">
-        <v>7058042</v>
+        <v>7057632</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125852447</v>
+        <v>125852445</v>
       </c>
       <c r="B17" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451341</v>
+        <v>451346</v>
       </c>
       <c r="R17" t="n">
-        <v>7058098</v>
+        <v>7058072</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2310,7 +2310,7 @@
         <v>125852465</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125852440</v>
+        <v>125852466</v>
       </c>
       <c r="B19" t="n">
-        <v>57652</v>
+        <v>78977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2420,21 +2420,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451296</v>
+        <v>451456</v>
       </c>
       <c r="R19" t="n">
-        <v>7057765</v>
+        <v>7058013</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125852463</v>
+        <v>125852440</v>
       </c>
       <c r="B20" t="n">
-        <v>91256</v>
+        <v>57656</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2522,21 +2522,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451524</v>
+        <v>451296</v>
       </c>
       <c r="R20" t="n">
-        <v>7057967</v>
+        <v>7057765</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2582,6 +2582,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2608,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125852466</v>
+        <v>125852463</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>91260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,21 +2624,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2643,10 +2648,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451456</v>
+        <v>451524</v>
       </c>
       <c r="R21" t="n">
-        <v>7058013</v>
+        <v>7057967</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2679,11 +2684,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2713,7 +2713,7 @@
         <v>125852461</v>
       </c>
       <c r="B22" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>125852462</v>
       </c>
       <c r="B23" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>125852451</v>
       </c>
       <c r="B24" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>125852459</v>
       </c>
       <c r="B25" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>125852439</v>
       </c>
       <c r="B26" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>126167777</v>
       </c>
       <c r="B27" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>126167776</v>
       </c>
       <c r="B28" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>126167782</v>
       </c>
       <c r="B29" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>126167783</v>
       </c>
       <c r="B30" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>126167784</v>
       </c>
       <c r="B31" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>126167778</v>
       </c>
       <c r="B32" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 23235-2025 artfynd.xlsx
+++ b/artfynd/A 23235-2025 artfynd.xlsx
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125852466</v>
+        <v>125852463</v>
       </c>
       <c r="B19" t="n">
-        <v>78977</v>
+        <v>91260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2420,21 +2420,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451456</v>
+        <v>451524</v>
       </c>
       <c r="R19" t="n">
-        <v>7058013</v>
+        <v>7057967</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2480,11 +2480,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2511,10 +2506,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125852440</v>
+        <v>125852466</v>
       </c>
       <c r="B20" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2522,21 +2517,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2546,10 +2541,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451296</v>
+        <v>451456</v>
       </c>
       <c r="R20" t="n">
-        <v>7057765</v>
+        <v>7058013</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2586,7 +2581,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2613,10 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125852463</v>
+        <v>125852440</v>
       </c>
       <c r="B21" t="n">
-        <v>91260</v>
+        <v>57656</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2624,21 +2619,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2648,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451524</v>
+        <v>451296</v>
       </c>
       <c r="R21" t="n">
-        <v>7057967</v>
+        <v>7057765</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2684,6 +2679,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 23235-2025 artfynd.xlsx
+++ b/artfynd/A 23235-2025 artfynd.xlsx
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125852446</v>
+        <v>125852449</v>
       </c>
       <c r="B5" t="n">
         <v>57656</v>
@@ -1009,17 +1009,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>besöker bebott bo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451310</v>
+        <v>451463</v>
       </c>
       <c r="R5" t="n">
-        <v>7058083</v>
+        <v>7057814</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål i gran, ca 2,5-3 upp. Ungar hördes och båda föräldrarna kom för att ge mat.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125852449</v>
+        <v>125852446</v>
       </c>
       <c r="B6" t="n">
         <v>57656</v>
@@ -1111,37 +1131,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>besöker bebott bo</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451463</v>
+        <v>451310</v>
       </c>
       <c r="R6" t="n">
-        <v>7057814</v>
+        <v>7058083</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Bohål i gran, ca 2,5-3 upp. Ungar hördes och båda föräldrarna kom för att ge mat.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125852453</v>
+        <v>125852452</v>
       </c>
       <c r="B8" t="n">
         <v>57656</v>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451364</v>
+        <v>451383</v>
       </c>
       <c r="R8" t="n">
-        <v>7057629</v>
+        <v>7057759</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125852452</v>
+        <v>125852453</v>
       </c>
       <c r="B9" t="n">
         <v>57656</v>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451383</v>
+        <v>451364</v>
       </c>
       <c r="R9" t="n">
-        <v>7057759</v>
+        <v>7057629</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125852437</v>
+        <v>125852445</v>
       </c>
       <c r="B12" t="n">
-        <v>91242</v>
+        <v>57656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451385</v>
+        <v>451346</v>
       </c>
       <c r="R12" t="n">
-        <v>7057764</v>
+        <v>7058072</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,6 +1771,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,7 +1802,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125852447</v>
+        <v>125852454</v>
       </c>
       <c r="B13" t="n">
         <v>57656</v>
@@ -1832,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451341</v>
+        <v>451369</v>
       </c>
       <c r="R13" t="n">
-        <v>7058098</v>
+        <v>7057632</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1904,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125852443</v>
+        <v>125852442</v>
       </c>
       <c r="B14" t="n">
         <v>57656</v>
@@ -1934,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451354</v>
+        <v>451256</v>
       </c>
       <c r="R14" t="n">
-        <v>7058042</v>
+        <v>7057974</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1974,7 +1979,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2001,7 +2006,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125852442</v>
+        <v>125852443</v>
       </c>
       <c r="B15" t="n">
         <v>57656</v>
@@ -2036,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451256</v>
+        <v>451354</v>
       </c>
       <c r="R15" t="n">
-        <v>7057974</v>
+        <v>7058042</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2076,7 +2081,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,7 +2108,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125852454</v>
+        <v>125852447</v>
       </c>
       <c r="B16" t="n">
         <v>57656</v>
@@ -2138,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451369</v>
+        <v>451341</v>
       </c>
       <c r="R16" t="n">
-        <v>7057632</v>
+        <v>7058098</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125852445</v>
+        <v>125852437</v>
       </c>
       <c r="B17" t="n">
-        <v>57656</v>
+        <v>91242</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2216,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2240,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451346</v>
+        <v>451385</v>
       </c>
       <c r="R17" t="n">
-        <v>7058072</v>
+        <v>7057764</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2276,11 +2281,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3006,10 +3006,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125852459</v>
+        <v>125852439</v>
       </c>
       <c r="B25" t="n">
-        <v>91260</v>
+        <v>57656</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3017,21 +3017,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3041,10 +3041,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451208</v>
+        <v>451296</v>
       </c>
       <c r="R25" t="n">
-        <v>7057705</v>
+        <v>7057721</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3077,6 +3077,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3103,10 +3108,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125852439</v>
+        <v>125852459</v>
       </c>
       <c r="B26" t="n">
-        <v>57656</v>
+        <v>91260</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3114,21 +3119,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3138,10 +3143,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451296</v>
+        <v>451208</v>
       </c>
       <c r="R26" t="n">
-        <v>7057721</v>
+        <v>7057705</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3174,11 +3179,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 23235-2025 artfynd.xlsx
+++ b/artfynd/A 23235-2025 artfynd.xlsx
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125852445</v>
+        <v>125852437</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
+        <v>91242</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451346</v>
+        <v>451385</v>
       </c>
       <c r="R12" t="n">
-        <v>7058072</v>
+        <v>7057764</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,11 +1771,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125852454</v>
+        <v>125852445</v>
       </c>
       <c r="B13" t="n">
         <v>57656</v>
@@ -1837,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451369</v>
+        <v>451346</v>
       </c>
       <c r="R13" t="n">
-        <v>7057632</v>
+        <v>7058072</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125852442</v>
+        <v>125852454</v>
       </c>
       <c r="B14" t="n">
         <v>57656</v>
@@ -1939,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451256</v>
+        <v>451369</v>
       </c>
       <c r="R14" t="n">
-        <v>7057974</v>
+        <v>7057632</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125852443</v>
+        <v>125852442</v>
       </c>
       <c r="B15" t="n">
         <v>57656</v>
@@ -2041,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451354</v>
+        <v>451256</v>
       </c>
       <c r="R15" t="n">
-        <v>7058042</v>
+        <v>7057974</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2081,7 +2076,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2108,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125852447</v>
+        <v>125852443</v>
       </c>
       <c r="B16" t="n">
         <v>57656</v>
@@ -2143,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451341</v>
+        <v>451354</v>
       </c>
       <c r="R16" t="n">
-        <v>7058098</v>
+        <v>7058042</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2183,7 +2178,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2210,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125852437</v>
+        <v>125852447</v>
       </c>
       <c r="B17" t="n">
-        <v>91242</v>
+        <v>57656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2221,21 +2216,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451385</v>
+        <v>451341</v>
       </c>
       <c r="R17" t="n">
-        <v>7057764</v>
+        <v>7058098</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2281,6 +2276,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3006,10 +3006,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125852439</v>
+        <v>125852459</v>
       </c>
       <c r="B25" t="n">
-        <v>57656</v>
+        <v>91260</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3017,21 +3017,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3041,10 +3041,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451296</v>
+        <v>451208</v>
       </c>
       <c r="R25" t="n">
-        <v>7057721</v>
+        <v>7057705</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3077,11 +3077,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3108,10 +3103,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125852459</v>
+        <v>125852439</v>
       </c>
       <c r="B26" t="n">
-        <v>91260</v>
+        <v>57656</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3119,21 +3114,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3143,10 +3138,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451208</v>
+        <v>451296</v>
       </c>
       <c r="R26" t="n">
-        <v>7057705</v>
+        <v>7057721</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3179,6 +3174,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 23235-2025 artfynd.xlsx
+++ b/artfynd/A 23235-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125852444</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125852448</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125852450</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>125852449</v>
       </c>
       <c r="B5" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>125852446</v>
       </c>
       <c r="B6" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>125852435</v>
       </c>
       <c r="B7" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>125852452</v>
       </c>
       <c r="B8" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>125852453</v>
       </c>
       <c r="B9" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>125852436</v>
       </c>
       <c r="B10" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>125852460</v>
       </c>
       <c r="B11" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125852437</v>
+        <v>125852445</v>
       </c>
       <c r="B12" t="n">
-        <v>91242</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451385</v>
+        <v>451346</v>
       </c>
       <c r="R12" t="n">
-        <v>7057764</v>
+        <v>7058072</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,6 +1771,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125852445</v>
+        <v>125852454</v>
       </c>
       <c r="B13" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1832,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451346</v>
+        <v>451369</v>
       </c>
       <c r="R13" t="n">
-        <v>7058072</v>
+        <v>7057632</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125852454</v>
+        <v>125852442</v>
       </c>
       <c r="B14" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1934,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451369</v>
+        <v>451256</v>
       </c>
       <c r="R14" t="n">
-        <v>7057632</v>
+        <v>7057974</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125852442</v>
+        <v>125852443</v>
       </c>
       <c r="B15" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451256</v>
+        <v>451354</v>
       </c>
       <c r="R15" t="n">
-        <v>7057974</v>
+        <v>7058042</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2076,7 +2081,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125852443</v>
+        <v>125852447</v>
       </c>
       <c r="B16" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451354</v>
+        <v>451341</v>
       </c>
       <c r="R16" t="n">
-        <v>7058042</v>
+        <v>7058098</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2178,7 +2183,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125852447</v>
+        <v>125852437</v>
       </c>
       <c r="B17" t="n">
-        <v>57656</v>
+        <v>91245</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2216,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2240,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451341</v>
+        <v>451385</v>
       </c>
       <c r="R17" t="n">
-        <v>7058098</v>
+        <v>7057764</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2276,11 +2281,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2310,7 +2310,7 @@
         <v>125852465</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>125852463</v>
       </c>
       <c r="B19" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>125852466</v>
       </c>
       <c r="B20" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>125852440</v>
       </c>
       <c r="B21" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>125852461</v>
       </c>
       <c r="B22" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>125852462</v>
       </c>
       <c r="B23" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>125852451</v>
       </c>
       <c r="B24" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125852459</v>
+        <v>125852439</v>
       </c>
       <c r="B25" t="n">
-        <v>91260</v>
+        <v>57657</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3017,21 +3017,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3041,10 +3041,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451208</v>
+        <v>451296</v>
       </c>
       <c r="R25" t="n">
-        <v>7057705</v>
+        <v>7057721</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3077,6 +3077,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3103,10 +3108,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125852439</v>
+        <v>125852459</v>
       </c>
       <c r="B26" t="n">
-        <v>57656</v>
+        <v>91263</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3114,21 +3119,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3138,10 +3143,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451296</v>
+        <v>451208</v>
       </c>
       <c r="R26" t="n">
-        <v>7057721</v>
+        <v>7057705</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3174,11 +3179,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3208,7 +3208,7 @@
         <v>126167777</v>
       </c>
       <c r="B27" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>126167776</v>
       </c>
       <c r="B28" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>126167782</v>
       </c>
       <c r="B29" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>126167783</v>
       </c>
       <c r="B30" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>126167784</v>
       </c>
       <c r="B31" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>126167778</v>
       </c>
       <c r="B32" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
